--- a/xls/square_high_un_16_tri3_20.xlsx
+++ b/xls/square_high_un_16_tri3_20.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <v>564</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18">
+        <v>340</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18">
+        <v>435</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>2388</v>
+      </c>
+      <c r="I18">
+        <v>-1.8824225498168043</v>
+      </c>
+      <c r="J18">
+        <v>-1.9805436812001675</v>
+      </c>
+      <c r="K18">
+        <v>-0.4910823650867202</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19">
+        <v>564</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <v>340</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>485</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19">
+        <v>2676</v>
+      </c>
+      <c r="I19">
+        <v>-1.9918047683539737</v>
+      </c>
+      <c r="J19">
+        <v>-1.6417383554023934</v>
+      </c>
+      <c r="K19">
+        <v>0.6167790424001789</v>
+      </c>
+    </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
         <v>11</v>
